--- a/data/trans_orig/IP40A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP40A-Edad-trans_orig.xlsx
@@ -849,7 +849,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5022</t>
+          <t>5262</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4532</t>
+          <t>5178</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7433</t>
+          <t>7583</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>713</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7040</t>
+          <t>6580</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8323</t>
+          <t>8262</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3560</t>
+          <t>3381</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12225</t>
+          <t>12213</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>6198</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16972</t>
+          <t>17020</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6818</t>
+          <t>6608</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17857</t>
+          <t>18670</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16699</t>
+          <t>15657</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33103</t>
+          <t>31041</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>13,98%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>18209</t>
+          <t>18046</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31902</t>
+          <t>33285</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18289</t>
+          <t>18777</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>33143</t>
+          <t>33568</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>40524</t>
+          <t>40459</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>61112</t>
+          <t>60784</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,38%</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>42329</t>
+          <t>42136</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>60040</t>
+          <t>59925</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1331,12 +1331,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24640</t>
+          <t>24724</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>40522</t>
+          <t>41254</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1366,12 +1366,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>71745</t>
+          <t>71553</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>94741</t>
+          <t>95791</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1381,12 +1381,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>43,14%</t>
         </is>
       </c>
     </row>
@@ -1409,12 +1409,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13851</t>
+          <t>13808</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27701</t>
+          <t>27157</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1424,12 +1424,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1444,12 +1444,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16818</t>
+          <t>17367</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31392</t>
+          <t>32217</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1459,12 +1459,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1479,12 +1479,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35646</t>
+          <t>34932</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55059</t>
+          <t>54011</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1494,12 +1494,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,33%</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>1367</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7494</t>
+          <t>7629</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1537,12 +1537,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1557,12 +1557,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2916</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10975</t>
+          <t>10890</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1592,12 +1592,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5714</t>
+          <t>5834</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>16162</t>
+          <t>15730</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1607,12 +1607,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4994</t>
+          <t>4703</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2539</t>
+          <t>3162</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1705,12 +1705,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>623</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5706</t>
+          <t>5992</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4431</t>
+          <t>3606</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3122</t>
+          <t>3614</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5379</t>
+          <t>4940</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -1978,12 +1978,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3160</t>
+          <t>3197</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11000</t>
+          <t>11983</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1993,12 +1993,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2013,12 +2013,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2228</t>
+          <t>2226</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10496</t>
+          <t>10296</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2048,12 +2048,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7123</t>
+          <t>7449</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>18635</t>
+          <t>18695</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2063,12 +2063,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -2091,12 +2091,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7544</t>
+          <t>7661</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18658</t>
+          <t>19238</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2106,12 +2106,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2126,12 +2126,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6292</t>
+          <t>6867</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17142</t>
+          <t>17667</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2141,12 +2141,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2161,12 +2161,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16933</t>
+          <t>16753</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32052</t>
+          <t>32071</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2204,12 +2204,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11398</t>
+          <t>12261</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24923</t>
+          <t>25283</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2219,12 +2219,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2239,12 +2239,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15988</t>
+          <t>15759</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30525</t>
+          <t>30074</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2254,12 +2254,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2274,12 +2274,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>31076</t>
+          <t>31338</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>50625</t>
+          <t>51286</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2289,12 +2289,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,21%</t>
         </is>
       </c>
     </row>
@@ -2317,12 +2317,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21191</t>
+          <t>21300</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>37500</t>
+          <t>37161</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2332,12 +2332,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>26244</t>
+          <t>26602</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>43404</t>
+          <t>44289</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2367,12 +2367,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2387,12 +2387,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>51333</t>
+          <t>51780</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>75763</t>
+          <t>75808</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2402,12 +2402,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,53%</t>
         </is>
       </c>
     </row>
@@ -2430,12 +2430,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>61615</t>
+          <t>62114</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>83131</t>
+          <t>84407</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2465,12 +2465,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>65293</t>
+          <t>65567</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>88409</t>
+          <t>89314</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>132354</t>
+          <t>132572</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>167090</t>
+          <t>165120</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>42,53%</t>
         </is>
       </c>
     </row>
@@ -2543,12 +2543,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>33085</t>
+          <t>31983</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>51716</t>
+          <t>50527</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2558,12 +2558,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>31119</t>
+          <t>31669</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>50542</t>
+          <t>50501</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>70417</t>
+          <t>68646</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>96286</t>
+          <t>95975</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,72%</t>
         </is>
       </c>
     </row>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2758</t>
+          <t>2779</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10880</t>
+          <t>10866</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2671,12 +2671,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2691,12 +2691,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3568</t>
+          <t>3710</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13583</t>
+          <t>13605</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2706,12 +2706,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2726,12 +2726,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>7535</t>
+          <t>7889</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>20210</t>
+          <t>20456</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2741,12 +2741,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -2769,12 +2769,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>676</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>6698</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2784,12 +2784,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5016</t>
+          <t>4771</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1330</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8463</t>
+          <t>8653</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2854,12 +2854,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6343</t>
+          <t>5385</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,7 +3039,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3787</t>
+          <t>3146</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6341</t>
+          <t>5779</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3414</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8531</t>
+          <t>8592</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1849</t>
+          <t>1622</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8821</t>
+          <t>9118</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3197,12 +3197,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -3225,12 +3225,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>2736</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>11936</t>
+          <t>11155</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3240,12 +3240,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>1389</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7934</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5900</t>
+          <t>6077</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>16635</t>
+          <t>16521</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -3338,12 +3338,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5550</t>
+          <t>5304</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>15683</t>
+          <t>15859</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>16221</t>
+          <t>15710</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>29941</t>
+          <t>29751</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>24247</t>
+          <t>24110</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>41454</t>
+          <t>41464</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,97%</t>
         </is>
       </c>
     </row>
@@ -3451,12 +3451,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>19900</t>
+          <t>19400</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>35556</t>
+          <t>35396</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>13812</t>
+          <t>13134</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>26944</t>
+          <t>26230</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>36734</t>
+          <t>36426</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>57391</t>
+          <t>56037</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>22,93%</t>
         </is>
       </c>
     </row>
@@ -3564,12 +3564,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>40850</t>
+          <t>41765</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>59891</t>
+          <t>59553</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3579,12 +3579,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3599,12 +3599,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>33905</t>
+          <t>33548</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>50237</t>
+          <t>50773</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3634,12 +3634,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>80589</t>
+          <t>80377</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>105277</t>
+          <t>103769</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>42,47%</t>
         </is>
       </c>
     </row>
@@ -3677,12 +3677,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>16559</t>
+          <t>16635</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>30693</t>
+          <t>30758</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3692,12 +3692,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3712,12 +3712,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>15216</t>
+          <t>14974</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>28822</t>
+          <t>28925</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>34534</t>
+          <t>34548</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>54733</t>
+          <t>55142</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,57%</t>
         </is>
       </c>
     </row>
@@ -3790,12 +3790,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2208</t>
+          <t>2646</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>9975</t>
+          <t>11158</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3805,12 +3805,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3589</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>12948</t>
+          <t>13433</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>7637</t>
+          <t>7665</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>20368</t>
+          <t>19589</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -3938,12 +3938,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5066</t>
+          <t>5139</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>577</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4987</t>
+          <t>5192</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>5413</t>
+          <t>4998</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4121</t>
+          <t>4289</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>705</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6859</t>
+          <t>6369</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>4431</t>
+          <t>5104</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4281,12 +4281,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>1895</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>9237</t>
+          <t>9083</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4296,12 +4296,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2821</t>
+          <t>2857</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>11642</t>
+          <t>11129</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -4359,12 +4359,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>2190</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>9632</t>
+          <t>10050</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4374,12 +4374,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2521</t>
+          <t>2538</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>10300</t>
+          <t>10121</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>6501</t>
+          <t>6074</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>16794</t>
+          <t>16778</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -4472,12 +4472,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>8881</t>
+          <t>9214</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>20516</t>
+          <t>20939</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4487,12 +4487,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>5954</t>
+          <t>5979</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>16197</t>
+          <t>16419</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>17759</t>
+          <t>17961</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>32837</t>
+          <t>32762</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,66%</t>
         </is>
       </c>
     </row>
@@ -4585,12 +4585,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>22740</t>
+          <t>23292</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>39195</t>
+          <t>39007</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4600,12 +4600,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>26929</t>
+          <t>26464</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>43375</t>
+          <t>43386</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>53929</t>
+          <t>53636</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>77100</t>
+          <t>77072</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,78%</t>
         </is>
       </c>
     </row>
@@ -4698,12 +4698,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>35976</t>
+          <t>35397</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>55120</t>
+          <t>53820</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4713,12 +4713,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>43517</t>
+          <t>43738</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>62773</t>
+          <t>61834</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>84618</t>
+          <t>84313</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>109867</t>
+          <t>110533</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>42,71%</t>
         </is>
       </c>
     </row>
@@ -4811,12 +4811,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>19318</t>
+          <t>19445</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>35647</t>
+          <t>34517</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4846,12 +4846,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>13549</t>
+          <t>13557</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>26845</t>
+          <t>26929</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4881,12 +4881,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>36149</t>
+          <t>36294</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>55379</t>
+          <t>56290</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,75%</t>
         </is>
       </c>
     </row>
@@ -4924,12 +4924,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>656</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>6108</t>
+          <t>6375</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4959,12 +4959,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>7954</t>
+          <t>8377</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4994,12 +4994,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>2587</t>
+          <t>2586</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>11561</t>
+          <t>11785</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5014,7 +5014,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -5077,7 +5077,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3442</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5092,7 +5092,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5112,7 +5112,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>3839</t>
+          <t>5113</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -5267,12 +5267,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>897</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>8936</t>
+          <t>8456</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>631</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>6405</t>
+          <t>5840</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2783</t>
+          <t>2848</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>11422</t>
+          <t>11694</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -5380,12 +5380,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>6113</t>
+          <t>6174</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>16628</t>
+          <t>16787</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5395,12 +5395,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5415,12 +5415,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>9843</t>
+          <t>10167</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>22231</t>
+          <t>23580</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5450,12 +5450,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>18324</t>
+          <t>18556</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>35441</t>
+          <t>35398</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>18960</t>
+          <t>19514</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>36676</t>
+          <t>36074</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5508,12 +5508,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5528,12 +5528,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>17633</t>
+          <t>17645</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>33551</t>
+          <t>33167</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>41751</t>
+          <t>39757</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>64566</t>
+          <t>62276</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -5606,12 +5606,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>42003</t>
+          <t>41733</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>65192</t>
+          <t>65308</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5621,12 +5621,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5641,12 +5641,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>56115</t>
+          <t>54857</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>80891</t>
+          <t>79890</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>103353</t>
+          <t>101356</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>137419</t>
+          <t>135742</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,19%</t>
         </is>
       </c>
     </row>
@@ -5719,12 +5719,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>96196</t>
+          <t>95905</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>127006</t>
+          <t>125975</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5734,12 +5734,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>98328</t>
+          <t>96014</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>128825</t>
+          <t>128125</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>202841</t>
+          <t>201771</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>245738</t>
+          <t>245662</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,06%</t>
         </is>
       </c>
     </row>
@@ -5832,12 +5832,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>201539</t>
+          <t>198937</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>240665</t>
+          <t>237181</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5847,12 +5847,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>185901</t>
+          <t>185699</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>221666</t>
+          <t>223984</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>395200</t>
+          <t>394895</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>448965</t>
+          <t>447175</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>40,16%</t>
         </is>
       </c>
     </row>
@@ -5945,12 +5945,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>97103</t>
+          <t>94676</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>126932</t>
+          <t>127466</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5960,12 +5960,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>89383</t>
+          <t>89393</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>120016</t>
+          <t>121063</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>196288</t>
+          <t>194631</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>239807</t>
+          <t>237737</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,35%</t>
         </is>
       </c>
     </row>
@@ -6058,12 +6058,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>11258</t>
+          <t>11648</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>25429</t>
+          <t>25561</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>17844</t>
+          <t>17280</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>34730</t>
+          <t>34791</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6108,12 +6108,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>31858</t>
+          <t>32018</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>52564</t>
+          <t>52626</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -6171,12 +6171,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>1344</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>8856</t>
+          <t>8576</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>9535</t>
+          <t>9120</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>4184</t>
+          <t>4219</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>14308</t>
+          <t>14226</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -6751,7 +6751,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4475</t>
+          <t>3831</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6781,12 +6781,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7389</t>
+          <t>7649</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1398</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8833</t>
+          <t>8750</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -6859,12 +6859,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>1096</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6936</t>
+          <t>6760</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2778</t>
+          <t>2749</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11253</t>
+          <t>10952</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5163</t>
+          <t>5140</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14637</t>
+          <t>14471</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -6972,12 +6972,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6931</t>
+          <t>7186</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17165</t>
+          <t>17192</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7007,12 +7007,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6403</t>
+          <t>6551</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16190</t>
+          <t>16730</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7042,12 +7042,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15625</t>
+          <t>15359</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29453</t>
+          <t>28768</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,45%</t>
         </is>
       </c>
     </row>
@@ -7085,12 +7085,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9090</t>
+          <t>9402</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19783</t>
+          <t>20053</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7120,12 +7120,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12904</t>
+          <t>13220</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25208</t>
+          <t>24953</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>25271</t>
+          <t>24867</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>41064</t>
+          <t>41775</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,98%</t>
         </is>
       </c>
     </row>
@@ -7198,12 +7198,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26144</t>
+          <t>26631</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>42000</t>
+          <t>40708</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7213,12 +7213,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7233,12 +7233,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22105</t>
+          <t>22682</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36907</t>
+          <t>37172</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7268,12 +7268,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>53015</t>
+          <t>53063</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>73718</t>
+          <t>73878</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7283,12 +7283,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>37,11%</t>
         </is>
       </c>
     </row>
@@ -7311,12 +7311,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21068</t>
+          <t>20704</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34473</t>
+          <t>35071</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7326,12 +7326,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7346,12 +7346,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19363</t>
+          <t>19019</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33901</t>
+          <t>33217</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7361,12 +7361,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7381,12 +7381,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43973</t>
+          <t>44410</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64175</t>
+          <t>65349</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7396,12 +7396,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,83%</t>
         </is>
       </c>
     </row>
@@ -7424,12 +7424,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4595</t>
+          <t>4460</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13395</t>
+          <t>12446</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1662</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7807</t>
+          <t>8007</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7474,12 +7474,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7494,12 +7494,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7476</t>
+          <t>7505</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18697</t>
+          <t>17785</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7509,12 +7509,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -7542,7 +7542,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3526</t>
+          <t>3295</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>802</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6439</t>
+          <t>7284</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7607,12 +7607,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7791</t>
+          <t>7629</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7622,12 +7622,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3544</t>
+          <t>3752</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7787,7 +7787,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4282</t>
+          <t>3772</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -7880,12 +7880,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9528</t>
+          <t>9538</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7167</t>
+          <t>7406</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7935,7 +7935,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7950,12 +7950,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4039</t>
+          <t>4032</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>13398</t>
+          <t>13879</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -7993,12 +7993,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5370</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14015</t>
+          <t>14367</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8008,12 +8008,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8028,12 +8028,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3805</t>
+          <t>3884</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12811</t>
+          <t>13610</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8043,12 +8043,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8063,12 +8063,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10694</t>
+          <t>10909</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23867</t>
+          <t>24030</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -8106,12 +8106,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6110</t>
+          <t>6339</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16053</t>
+          <t>16048</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8141,12 +8141,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13116</t>
+          <t>12592</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27102</t>
+          <t>25534</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8156,12 +8156,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8176,12 +8176,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>22751</t>
+          <t>21872</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>40215</t>
+          <t>39138</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,7%</t>
         </is>
       </c>
     </row>
@@ -8219,12 +8219,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20762</t>
+          <t>20669</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>35059</t>
+          <t>34839</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8234,12 +8234,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28648</t>
+          <t>27752</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>46904</t>
+          <t>45802</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8269,12 +8269,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>52560</t>
+          <t>52349</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>76375</t>
+          <t>75638</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,67%</t>
         </is>
       </c>
     </row>
@@ -8332,12 +8332,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>46963</t>
+          <t>46854</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>66340</t>
+          <t>65985</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8347,12 +8347,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8367,12 +8367,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>57717</t>
+          <t>57687</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>79394</t>
+          <t>79742</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8402,12 +8402,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>108475</t>
+          <t>110190</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>138055</t>
+          <t>137877</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>37,68%</t>
         </is>
       </c>
     </row>
@@ -8445,12 +8445,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>30344</t>
+          <t>30606</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>47537</t>
+          <t>47443</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8460,12 +8460,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8480,12 +8480,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>42319</t>
+          <t>43012</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>63308</t>
+          <t>65023</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8495,12 +8495,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8515,12 +8515,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>78614</t>
+          <t>79013</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>105243</t>
+          <t>105199</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,75%</t>
         </is>
       </c>
     </row>
@@ -8558,12 +8558,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5570</t>
+          <t>5528</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>15164</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8573,12 +8573,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8593,12 +8593,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>10970</t>
+          <t>11024</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>23647</t>
+          <t>23287</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8608,12 +8608,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>19284</t>
+          <t>18587</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>35117</t>
+          <t>34991</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,56%</t>
         </is>
       </c>
     </row>
@@ -8671,12 +8671,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9075</t>
+          <t>9053</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8686,12 +8686,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8706,12 +8706,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>669</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>6565</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8721,12 +8721,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8741,12 +8741,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3419</t>
+          <t>3757</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12431</t>
+          <t>12503</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -8906,7 +8906,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3717</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3816</t>
+          <t>3403</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4768</t>
+          <t>4821</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8991,7 +8991,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -9014,12 +9014,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>584</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5661</t>
+          <t>5411</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9034,7 +9034,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9049,12 +9049,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>684</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7694</t>
+          <t>6835</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9064,12 +9064,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9084,12 +9084,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2052</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>10101</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9099,12 +9099,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -9127,12 +9127,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2155</t>
+          <t>2299</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10387</t>
+          <t>11317</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2893</t>
+          <t>2959</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>11791</t>
+          <t>11326</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7002</t>
+          <t>7075</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>18918</t>
+          <t>18674</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9212,12 +9212,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -9240,12 +9240,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>8628</t>
+          <t>8371</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>20234</t>
+          <t>20434</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>9112</t>
+          <t>9765</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>22318</t>
+          <t>21624</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9310,12 +9310,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>21128</t>
+          <t>20640</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>38120</t>
+          <t>37291</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9325,12 +9325,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,45%</t>
         </is>
       </c>
     </row>
@@ -9353,12 +9353,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>21465</t>
+          <t>20646</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>38135</t>
+          <t>37209</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9368,12 +9368,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9388,12 +9388,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>18020</t>
+          <t>17509</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>33627</t>
+          <t>32343</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9403,12 +9403,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>42925</t>
+          <t>43506</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>64413</t>
+          <t>65224</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,77%</t>
         </is>
       </c>
     </row>
@@ -9466,12 +9466,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>29812</t>
+          <t>32104</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>49175</t>
+          <t>51498</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9481,12 +9481,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>41675</t>
+          <t>41934</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>61705</t>
+          <t>61844</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9516,12 +9516,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -9536,12 +9536,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>77576</t>
+          <t>78539</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>104912</t>
+          <t>103994</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -9551,12 +9551,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,71%</t>
         </is>
       </c>
     </row>
@@ -9579,12 +9579,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>34949</t>
+          <t>34562</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>54038</t>
+          <t>53262</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9594,12 +9594,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9614,12 +9614,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>26781</t>
+          <t>26483</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>44170</t>
+          <t>44006</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -9629,12 +9629,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -9649,12 +9649,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>67671</t>
+          <t>66350</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>92198</t>
+          <t>91716</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -9664,12 +9664,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,62%</t>
         </is>
       </c>
     </row>
@@ -9692,12 +9692,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>9068</t>
+          <t>8616</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>20289</t>
+          <t>20034</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -9727,12 +9727,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>5773</t>
+          <t>5750</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>16016</t>
+          <t>16869</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -9742,12 +9742,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -9762,12 +9762,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>16603</t>
+          <t>16488</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>32158</t>
+          <t>31508</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -9777,12 +9777,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -9805,12 +9805,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>1583</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>8340</t>
+          <t>8008</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -9840,12 +9840,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>587</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5667</t>
+          <t>5544</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -9860,7 +9860,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -9875,12 +9875,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2900</t>
+          <t>2689</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>11529</t>
+          <t>10978</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9890,12 +9890,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -10040,7 +10040,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2622</t>
+          <t>3949</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -10110,7 +10110,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2846</t>
+          <t>3262</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -10125,7 +10125,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -10153,7 +10153,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>4286</t>
+          <t>4329</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10168,7 +10168,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10183,12 +10183,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>650</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>6069</t>
+          <t>6492</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10218,12 +10218,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>7981</t>
+          <t>8421</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -10266,7 +10266,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4779</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10281,7 +10281,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10296,12 +10296,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2202</t>
+          <t>2182</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>9623</t>
+          <t>10080</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10311,12 +10311,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10331,12 +10331,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3606</t>
+          <t>3070</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>12863</t>
+          <t>12514</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10346,12 +10346,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -10374,12 +10374,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>10034</t>
+          <t>10136</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>23306</t>
+          <t>22425</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10409,12 +10409,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>7659</t>
+          <t>7886</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>19956</t>
+          <t>19504</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -10424,12 +10424,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10444,12 +10444,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>20419</t>
+          <t>20353</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>38939</t>
+          <t>37172</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10459,12 +10459,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>13,93%</t>
         </is>
       </c>
     </row>
@@ -10487,12 +10487,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>14952</t>
+          <t>15390</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>28813</t>
+          <t>29359</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -10502,12 +10502,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -10522,12 +10522,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>20997</t>
+          <t>20663</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>37018</t>
+          <t>38465</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -10537,12 +10537,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -10557,12 +10557,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>39066</t>
+          <t>39766</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>59516</t>
+          <t>61855</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -10572,12 +10572,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>23,17%</t>
         </is>
       </c>
     </row>
@@ -10600,12 +10600,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>37250</t>
+          <t>37784</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>56470</t>
+          <t>55655</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -10615,12 +10615,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -10635,12 +10635,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>29315</t>
+          <t>29033</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>46981</t>
+          <t>47387</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -10650,12 +10650,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -10670,12 +10670,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>71968</t>
+          <t>72541</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>96953</t>
+          <t>98490</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -10685,12 +10685,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,9%</t>
         </is>
       </c>
     </row>
@@ -10713,12 +10713,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>29410</t>
+          <t>29172</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>47344</t>
+          <t>46975</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -10728,12 +10728,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>29737</t>
+          <t>28466</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>47291</t>
+          <t>47017</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>62802</t>
+          <t>63588</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>87743</t>
+          <t>87089</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,63%</t>
         </is>
       </c>
     </row>
@@ -10826,12 +10826,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>6490</t>
+          <t>7199</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -10846,7 +10846,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -10861,12 +10861,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>7845</t>
+          <t>8421</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>19386</t>
+          <t>20802</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>11102</t>
+          <t>10386</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>24779</t>
+          <t>23692</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -10944,7 +10944,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>5769</t>
+          <t>6472</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10959,7 +10959,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11014,7 +11014,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>6083</t>
+          <t>6035</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11029,7 +11029,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -11169,12 +11169,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>640</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>5582</t>
+          <t>5427</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -11189,7 +11189,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -11209,7 +11209,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>4289</t>
+          <t>5089</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -11239,12 +11239,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>751</t>
+          <t>749</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>6953</t>
+          <t>7105</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -11259,7 +11259,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -11282,12 +11282,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>4443</t>
+          <t>4642</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>14314</t>
+          <t>15102</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -11297,12 +11297,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -11317,12 +11317,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>7238</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>18034</t>
+          <t>18476</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -11332,12 +11332,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -11352,12 +11352,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>13793</t>
+          <t>14031</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>29407</t>
+          <t>30111</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -11367,12 +11367,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -11395,12 +11395,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>12921</t>
+          <t>12576</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>27061</t>
+          <t>26762</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11410,12 +11410,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11430,12 +11430,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>18108</t>
+          <t>17458</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>34230</t>
+          <t>34413</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>34131</t>
+          <t>34992</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>56290</t>
+          <t>55499</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -11508,12 +11508,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>40592</t>
+          <t>40751</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>62437</t>
+          <t>61818</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -11523,12 +11523,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11543,12 +11543,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>46125</t>
+          <t>46273</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>70151</t>
+          <t>70543</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>91944</t>
+          <t>93199</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>125962</t>
+          <t>126014</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -11621,12 +11621,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>77985</t>
+          <t>78569</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>106561</t>
+          <t>105691</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -11636,12 +11636,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -11656,12 +11656,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>94111</t>
+          <t>93099</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>123676</t>
+          <t>124571</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>179414</t>
+          <t>179569</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>221789</t>
+          <t>223157</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,72%</t>
         </is>
       </c>
     </row>
@@ -11734,12 +11734,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>157338</t>
+          <t>159078</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>192822</t>
+          <t>193423</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -11749,12 +11749,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -11769,12 +11769,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>168403</t>
+          <t>167059</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>204945</t>
+          <t>202418</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>336395</t>
+          <t>337893</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>386624</t>
+          <t>388769</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,36%</t>
         </is>
       </c>
     </row>
@@ -11847,12 +11847,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>130426</t>
+          <t>131495</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>163272</t>
+          <t>164304</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -11862,12 +11862,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -11882,12 +11882,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>134099</t>
+          <t>133631</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>169600</t>
+          <t>169380</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>275220</t>
+          <t>275038</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>321464</t>
+          <t>322625</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,51%</t>
         </is>
       </c>
     </row>
@@ -11960,12 +11960,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>25978</t>
+          <t>26320</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>45029</t>
+          <t>43406</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -11975,12 +11975,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>33540</t>
+          <t>34749</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>54808</t>
+          <t>54999</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -12010,12 +12010,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>65303</t>
+          <t>63427</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>93595</t>
+          <t>93209</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,24%</t>
         </is>
       </c>
     </row>
@@ -12073,12 +12073,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>6179</t>
+          <t>5926</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>16941</t>
+          <t>17500</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12088,12 +12088,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12108,12 +12108,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>3735</t>
+          <t>3590</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>12490</t>
+          <t>13181</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12123,12 +12123,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>12271</t>
+          <t>11695</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>26881</t>
+          <t>25245</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12158,12 +12158,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
